--- a/듀링 법인차량 현황 ver.2.0.xlsx
+++ b/듀링 법인차량 현황 ver.2.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\during-car-qr-main\during-car-qr-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2438760-FDC5-4DA2-86A3-FBEC7E4F5A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{798DDC96-BF09-4C76-A81C-27A871D83311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="법인차량현황" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="238">
   <si>
     <t>차종</t>
   </si>
@@ -298,10 +298,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>에치에스 모터스</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>차량세차</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -319,10 +315,6 @@
   </si>
   <si>
     <t>그랜저 하이브리드</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>에치에스 모터스</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1004,6 +996,14 @@
   </si>
   <si>
     <t>1588-5656</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>엔진오일, 타이어 4EA 교체</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>에이치에스 모터스</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1351,7 +1351,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1650,9 +1650,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2046,7 +2043,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C1" s="20" t="s">
         <v>21</v>
@@ -2055,31 +2052,31 @@
         <v>0</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F1" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="G1" s="20" t="s">
-        <v>168</v>
-      </c>
       <c r="H1" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="J1" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="L1" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="M1" s="21" t="s">
         <v>182</v>
-      </c>
-      <c r="J1" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="K1" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="L1" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="M1" s="21" t="s">
-        <v>184</v>
       </c>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
@@ -2090,10 +2087,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>40</v>
@@ -2102,16 +2099,16 @@
         <v>5</v>
       </c>
       <c r="F2" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="G2" s="22" t="s">
         <v>167</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>169</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>34</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J2" s="25">
         <v>46836</v>
@@ -2133,28 +2130,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>39</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F3" s="19" t="s">
         <v>59</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H3" s="22" t="s">
         <v>35</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J3" s="29">
         <v>46408</v>
@@ -2176,28 +2173,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>41</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F4" s="19" t="s">
         <v>59</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H4" s="22" t="s">
         <v>35</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J4" s="29">
         <v>46520</v>
@@ -2219,10 +2216,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>42</v>
@@ -2234,13 +2231,13 @@
         <v>38</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H5" s="26" t="s">
         <v>34</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J5" s="29">
         <v>46474</v>
@@ -2262,10 +2259,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>42</v>
@@ -2277,13 +2274,13 @@
         <v>59</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H6" s="22" t="s">
         <v>35</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J6" s="29">
         <v>46491</v>
@@ -2305,10 +2302,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>37</v>
@@ -2320,13 +2317,13 @@
         <v>38</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="H7" s="100" t="s">
+        <v>174</v>
+      </c>
+      <c r="H7" s="26" t="s">
         <v>48</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J7" s="29">
         <v>46403</v>
@@ -2344,10 +2341,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>37</v>
@@ -2359,13 +2356,13 @@
         <v>38</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H8" s="26" t="s">
         <v>48</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J8" s="29">
         <v>46403</v>
@@ -2382,10 +2379,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>42</v>
@@ -2397,13 +2394,13 @@
         <v>38</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="H9" s="100" t="s">
+        <v>174</v>
+      </c>
+      <c r="H9" s="26" t="s">
         <v>48</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J9" s="29">
         <v>46403</v>
@@ -2421,10 +2418,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>57</v>
@@ -2436,13 +2433,13 @@
         <v>38</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J10" s="29">
         <v>46408</v>
@@ -2460,28 +2457,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D11" s="35" t="s">
         <v>58</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F11" s="19" t="s">
         <v>59</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J11" s="85">
         <v>46210</v>
@@ -2499,13 +2496,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E12" s="19" t="s">
         <v>5</v>
@@ -2514,13 +2511,13 @@
         <v>59</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I12" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J12" s="25">
         <v>46744</v>
@@ -2542,28 +2539,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F13" s="19" t="s">
         <v>38</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H13" s="26" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J13" s="29">
         <v>47847</v>
@@ -2585,28 +2582,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" s="88" t="s">
+        <v>225</v>
+      </c>
+      <c r="D14" s="88" t="s">
         <v>226</v>
       </c>
-      <c r="C14" s="88" t="s">
+      <c r="E14" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="D14" s="88" t="s">
+      <c r="F14" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="G14" s="26" t="s">
         <v>228</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="F14" s="19" t="s">
+      <c r="H14" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="I14" s="18" t="s">
         <v>231</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="H14" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>233</v>
       </c>
       <c r="J14" s="29">
         <v>47903</v>
@@ -2671,7 +2668,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C2:E13 A2:B17 F8:K8 M8 C14:D14 E14:E17 F2:M7 F9:M17">
+  <conditionalFormatting sqref="F2:M7 C2:E13 A2:B17 F8:K8 M8 F9:M17 C14:D14 E14:E17">
     <cfRule type="expression" dxfId="5" priority="11">
       <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
     </cfRule>
@@ -2709,22 +2706,22 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="20" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C1" s="20" t="s">
         <v>21</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E1" s="20" t="s">
         <v>22</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G1" s="20" t="s">
         <v>23</v>
@@ -2738,10 +2735,10 @@
         <v>45854</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D2" s="33" t="s">
         <v>50</v>
@@ -2762,10 +2759,10 @@
         <v>45855</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D3" s="33" t="s">
         <v>55</v>
@@ -2786,10 +2783,10 @@
         <v>45883</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>43</v>
@@ -2812,10 +2809,10 @@
         <v>45888</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>54</v>
@@ -2836,10 +2833,10 @@
         <v>45890</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>45</v>
@@ -2860,10 +2857,10 @@
         <v>45915</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>60</v>
@@ -2884,10 +2881,10 @@
         <v>45975</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>62</v>
@@ -2896,7 +2893,7 @@
         <v>35734</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>63</v>
+        <v>237</v>
       </c>
       <c r="G8" s="9">
         <v>110000</v>
@@ -2908,10 +2905,10 @@
         <v>46028</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>62</v>
@@ -2920,7 +2917,7 @@
         <v>136233</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>69</v>
+        <v>237</v>
       </c>
       <c r="G9" s="9">
         <v>105000</v>
@@ -2932,10 +2929,10 @@
         <v>46043</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>60</v>
@@ -2956,10 +2953,10 @@
         <v>46050</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>60</v>
@@ -2980,19 +2977,19 @@
         <v>46105</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E12" s="87">
         <v>175843</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G12" s="9">
         <v>350000</v>
@@ -3000,23 +2997,51 @@
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="9"/>
+      <c r="A13" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="87">
+        <v>77785</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="9">
+        <v>185284</v>
+      </c>
       <c r="H13" s="8"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="9"/>
+      <c r="A14" s="10">
+        <v>46188</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="E14" s="87">
+        <v>60381</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="G14" s="9">
+        <v>630000</v>
+      </c>
       <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
@@ -3826,7 +3851,7 @@
       <formula>#REF!="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:C12">
+  <conditionalFormatting sqref="C11:C13">
     <cfRule type="expression" dxfId="1" priority="3">
       <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
     </cfRule>
@@ -3835,7 +3860,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C10 C13:C92" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C10 C14:C92" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>차량번호</formula1>
     </dataValidation>
   </dataValidations>
@@ -3869,26 +3894,26 @@
   <sheetData>
     <row r="9" spans="3:35" x14ac:dyDescent="0.4">
       <c r="AA9" s="98" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AB9" s="96" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC9" s="59"/>
       <c r="AD9" s="37" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AE9" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF9" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG9" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="AH9" s="37" t="s">
         <v>77</v>
-      </c>
-      <c r="AF9" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="AG9" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH9" s="37" t="s">
-        <v>79</v>
       </c>
       <c r="AI9" s="43" t="s">
         <v>58</v>
@@ -3896,65 +3921,65 @@
     </row>
     <row r="10" spans="3:35" x14ac:dyDescent="0.4">
       <c r="C10" s="61" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D10" s="62" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="62" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="62" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="62" t="s">
+      <c r="H10" s="63" t="s">
         <v>72</v>
-      </c>
-      <c r="F10" s="62" t="s">
-        <v>82</v>
-      </c>
-      <c r="G10" s="62" t="s">
-        <v>73</v>
-      </c>
-      <c r="H10" s="63" t="s">
-        <v>74</v>
       </c>
       <c r="I10" s="79"/>
       <c r="K10" s="58" t="s">
+        <v>90</v>
+      </c>
+      <c r="L10" s="59" t="s">
         <v>92</v>
       </c>
-      <c r="L10" s="59" t="s">
-        <v>94</v>
-      </c>
       <c r="M10" s="60" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="O10" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="P10" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="P10" s="59" t="s">
+      <c r="Q10" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="R10" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="Q10" s="59" t="s">
+      <c r="S10" s="59" t="s">
         <v>107</v>
       </c>
-      <c r="R10" s="59" t="s">
+      <c r="T10" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="S10" s="59" t="s">
+      <c r="U10" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="T10" s="59" t="s">
+      <c r="V10" s="59" t="s">
         <v>110</v>
       </c>
-      <c r="U10" s="59" t="s">
+      <c r="W10" s="59" t="s">
         <v>111</v>
       </c>
-      <c r="V10" s="59" t="s">
+      <c r="X10" s="59" t="s">
         <v>112</v>
       </c>
-      <c r="W10" s="59" t="s">
+      <c r="Y10" s="60" t="s">
         <v>113</v>
-      </c>
-      <c r="X10" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y10" s="60" t="s">
-        <v>115</v>
       </c>
       <c r="AA10" s="99"/>
       <c r="AB10" s="97"/>
@@ -3963,13 +3988,13 @@
         <v>36</v>
       </c>
       <c r="AE10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AF10" t="s">
         <v>47</v>
       </c>
       <c r="AG10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AH10" t="s">
         <v>49</v>
@@ -3983,13 +4008,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
         <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G11" s="45">
         <v>2497</v>
@@ -3999,16 +4024,16 @@
       </c>
       <c r="I11" s="80"/>
       <c r="K11" s="95" t="s">
+        <v>91</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="M11" s="56" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O11" s="47" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="P11" s="65">
         <v>0.05</v>
@@ -4044,10 +4069,10 @@
         <v>1</v>
       </c>
       <c r="AB11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AC11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AD11" s="67">
         <v>2497</v>
@@ -4073,13 +4098,13 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G12" s="45">
         <v>180</v>
@@ -4090,19 +4115,19 @@
       <c r="I12" s="80"/>
       <c r="K12" s="95"/>
       <c r="L12" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M12" s="56" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AA12" s="44">
         <v>2</v>
       </c>
       <c r="AB12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AC12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AD12">
         <v>200</v>
@@ -4120,13 +4145,13 @@
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
         <v>47</v>
       </c>
       <c r="F13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G13" s="45">
         <v>180</v>
@@ -4137,19 +4162,19 @@
       <c r="I13" s="80"/>
       <c r="K13" s="95"/>
       <c r="L13" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M13" s="56" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AA13" s="44">
         <v>3</v>
       </c>
       <c r="AB13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AD13" s="45">
         <f>AD11*AD12</f>
@@ -4178,13 +4203,13 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G14" s="45">
         <v>1999</v>
@@ -4195,19 +4220,19 @@
       <c r="I14" s="80"/>
       <c r="K14" s="91"/>
       <c r="L14" s="41" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M14" s="57" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AA14" s="44">
         <v>4</v>
       </c>
       <c r="AB14" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AC14" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AD14" s="69">
         <v>1</v>
@@ -4233,13 +4258,13 @@
         <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
         <v>49</v>
       </c>
       <c r="F15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G15" s="45">
         <v>1591</v>
@@ -4252,10 +4277,10 @@
         <v>5</v>
       </c>
       <c r="AB15" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AC15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AD15" s="45">
         <v>499400</v>
@@ -4289,7 +4314,7 @@
         <v>56</v>
       </c>
       <c r="F16" s="48" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G16" s="49">
         <v>111</v>
@@ -4302,10 +4327,10 @@
         <v>8</v>
       </c>
       <c r="AB16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AC16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AD16" s="69">
         <v>0.3</v>
@@ -4331,10 +4356,10 @@
         <v>9</v>
       </c>
       <c r="AB17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AC17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AD17" s="71">
         <f>AD15*0.3</f>
@@ -4363,10 +4388,10 @@
         <v>10</v>
       </c>
       <c r="AB18" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AC18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AD18" s="74">
         <v>29710</v>
@@ -4392,10 +4417,10 @@
         <v>11</v>
       </c>
       <c r="AB19" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AC19" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AD19" s="77">
         <f>AD15+AD17-AD18</f>
@@ -4424,22 +4449,22 @@
     </row>
     <row r="20" spans="3:35" x14ac:dyDescent="0.4">
       <c r="C20" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="62" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="62" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" s="62" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="62" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="62" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="62" t="s">
-        <v>89</v>
-      </c>
       <c r="G20" s="62" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" s="63" t="s">
         <v>88</v>
-      </c>
-      <c r="H20" s="63" t="s">
-        <v>90</v>
       </c>
       <c r="I20" s="79"/>
       <c r="AA20" s="37"/>
@@ -4457,7 +4482,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s">
         <v>36</v>
@@ -4481,10 +4506,10 @@
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F22" s="45">
         <v>95420</v>
@@ -4508,7 +4533,7 @@
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E23" t="s">
         <v>47</v>
@@ -4531,10 +4556,10 @@
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F24" s="45">
         <v>305200</v>
@@ -4554,7 +4579,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E25" t="s">
         <v>49</v>
@@ -4595,7 +4620,7 @@
     </row>
     <row r="27" spans="3:35" x14ac:dyDescent="0.4">
       <c r="C27" s="93" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D27" s="94"/>
       <c r="E27" s="94"/>
@@ -4615,13 +4640,13 @@
     </row>
     <row r="30" spans="3:35" x14ac:dyDescent="0.4">
       <c r="C30" s="58" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D30" s="59" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E30" s="59" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F30" s="59">
         <v>2024</v>
@@ -4633,13 +4658,13 @@
         <v>2026</v>
       </c>
       <c r="I30" s="59" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J30" s="59" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K30" s="63" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="3:35" x14ac:dyDescent="0.4">
@@ -4647,7 +4672,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>36</v>
@@ -4661,13 +4686,13 @@
         <v>619510</v>
       </c>
       <c r="I31" s="84" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J31" s="83" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K31" s="51" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="3:35" x14ac:dyDescent="0.4">
@@ -4675,10 +4700,10 @@
         <v>2</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F32" s="40"/>
       <c r="G32" s="40">
@@ -4688,13 +4713,13 @@
         <v>124040</v>
       </c>
       <c r="I32" s="40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K32" s="51" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="3:11" x14ac:dyDescent="0.4">
@@ -4702,7 +4727,7 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>47</v>
@@ -4715,13 +4740,13 @@
         <v>124040</v>
       </c>
       <c r="I33" s="40" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K33" s="51" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="3:11" x14ac:dyDescent="0.4">
@@ -4729,10 +4754,10 @@
         <v>4</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F34" s="40">
         <v>34680</v>
@@ -4744,10 +4769,10 @@
         <v>396760</v>
       </c>
       <c r="I34" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K34" s="51"/>
     </row>
@@ -4756,7 +4781,7 @@
         <v>5</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>49</v>
@@ -4771,10 +4796,10 @@
         <v>172690</v>
       </c>
       <c r="I35" s="40" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K35" s="51"/>
     </row>
@@ -4807,7 +4832,7 @@
     </row>
     <row r="37" spans="3:11" x14ac:dyDescent="0.4">
       <c r="C37" s="91" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D37" s="92"/>
       <c r="E37" s="92"/>
@@ -4824,10 +4849,10 @@
         <v>1837710</v>
       </c>
       <c r="I37" s="82" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J37" s="82" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K37" s="52"/>
     </row>
@@ -4963,7 +4988,7 @@
         <v>10</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J8" s="4"/>
     </row>
